--- a/capas/SEA_Atacama_Proyectos.xlsx
+++ b/capas/SEA_Atacama_Proyectos.xlsx
@@ -5354,6 +5354,7 @@
     <col min="1" max="1" width="68.8888888888889" customWidth="1"/>
     <col min="2" max="2" width="85.8888888888889" customWidth="1"/>
     <col min="11" max="11" width="18.8888888888889" customWidth="1"/>
+    <col min="12" max="12" width="16.2222222222222" customWidth="1"/>
     <col min="13" max="13" width="17.4444444444444" customWidth="1"/>
   </cols>
   <sheetData>

--- a/capas/SEA_Atacama_Proyectos.xlsx
+++ b/capas/SEA_Atacama_Proyectos.xlsx
@@ -1064,12 +1064,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P516"/>
+  <dimension ref="A1:Q516"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col width="68.8888888888889" customWidth="1" min="1" max="1"/>
     <col width="85.8888888888889" customWidth="1" min="2" max="2"/>
     <col width="18.8888888888889" customWidth="1" min="11" max="11"/>
+    <col width="16.2222222222222" customWidth="1" min="12" max="12"/>
     <col width="17.4444444444444" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
@@ -1131,7 +1132,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>Estado del Proyecto</t>
+          <t>Estado</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
@@ -1152,6 +1153,11 @@
       <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Longitud Punto Representativo</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>documentacion</t>
         </is>
       </c>
     </row>
@@ -1224,6 +1230,11 @@
       <c r="P2" t="n">
         <v>-70.067031</v>
       </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2166507479</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1294,6 +1305,11 @@
       <c r="P3" t="n">
         <v>-70.067031</v>
       </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2166745393</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1364,6 +1380,11 @@
       <c r="P4" t="n">
         <v>-70.067031</v>
       </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2166722539</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1434,6 +1455,11 @@
       <c r="P5" t="n">
         <v>-70.067031</v>
       </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2166458691</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1504,6 +1530,11 @@
       <c r="P6" t="n">
         <v>-70.742637</v>
       </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2166274575</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1574,6 +1605,11 @@
       <c r="P7" t="n">
         <v>-70.809307</v>
       </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2166248414</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1644,6 +1680,11 @@
       <c r="P8" t="n">
         <v>-69.951019</v>
       </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2166109337</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1714,6 +1755,11 @@
       <c r="P9" t="n">
         <v>-70.82138</v>
       </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2166144379</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1784,6 +1830,11 @@
       <c r="P10" t="n">
         <v>-70.201517</v>
       </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2166144423</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1854,6 +1905,11 @@
       <c r="P11" t="n">
         <v>-69.875489</v>
       </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2166144374</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1924,6 +1980,11 @@
       <c r="P12" t="n">
         <v>-70.09821599999999</v>
       </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2165874135</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1994,6 +2055,11 @@
       <c r="P13" t="n">
         <v>-69.42113202</v>
       </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2165785991</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2064,6 +2130,11 @@
       <c r="P14" t="n">
         <v>-70.29317899999999</v>
       </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2165787805</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2134,6 +2205,11 @@
       <c r="P15" t="n">
         <v>-70.86640800000001</v>
       </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2165741637</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2204,6 +2280,11 @@
       <c r="P16" t="n">
         <v>-70.685582</v>
       </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2165636114</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2274,6 +2355,11 @@
       <c r="P17" t="n">
         <v>-70.294589</v>
       </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2165437199</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2344,6 +2430,11 @@
       <c r="P18" t="n">
         <v>-69.330749</v>
       </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2165222793</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2414,6 +2505,11 @@
       <c r="P19" t="n">
         <v>-70.362369</v>
       </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2165064797</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2484,6 +2580,11 @@
       <c r="P20" t="n">
         <v>-70.986439</v>
       </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2164840175</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2554,6 +2655,11 @@
       <c r="P21" t="n">
         <v>-70.252979</v>
       </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2164626901</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2624,6 +2730,11 @@
       <c r="P22" t="n">
         <v>-70.067031</v>
       </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2164608901</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2694,6 +2805,11 @@
       <c r="P23" t="n">
         <v>-70.736144</v>
       </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2164580331</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2764,6 +2880,11 @@
       <c r="P24" t="n">
         <v>-70.327234</v>
       </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2164222251</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2834,6 +2955,11 @@
       <c r="P25" t="n">
         <v>-70.918902</v>
       </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2164207820</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2904,6 +3030,11 @@
       <c r="P26" t="n">
         <v>-70.816614</v>
       </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2164006601</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2974,6 +3105,11 @@
       <c r="P27" t="n">
         <v>-70.806842</v>
       </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2163940105</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -3046,6 +3182,11 @@
       <c r="P28" t="n">
         <v>-70.09688199999999</v>
       </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2164048370</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -3116,6 +3257,11 @@
       <c r="P29" t="n">
         <v>-70.201677</v>
       </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2163991783</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -3186,6 +3332,11 @@
       <c r="P30" t="n">
         <v>-69.874954</v>
       </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2164006752</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -3256,6 +3407,11 @@
       <c r="P31" t="n">
         <v>-70.532825</v>
       </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2163941262</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -3328,6 +3484,11 @@
       <c r="P32" t="n">
         <v>-70.44787100000001</v>
       </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2163984852</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -3400,6 +3561,11 @@
       <c r="P33" t="n">
         <v>-70.935824</v>
       </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2163895353</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -3470,6 +3636,11 @@
       <c r="P34" t="n">
         <v>-70.02905199999999</v>
       </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2163910197</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -3542,6 +3713,11 @@
       <c r="P35" t="n">
         <v>-70.770034</v>
       </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2163818625</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -3614,6 +3790,11 @@
       <c r="P36" t="n">
         <v>-69.3921</v>
       </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2163682394</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -3686,6 +3867,11 @@
       <c r="P37" t="n">
         <v>-70.245878</v>
       </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2163225794</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -3758,6 +3944,11 @@
       <c r="P38" t="n">
         <v>-70.59395000000001</v>
       </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2163354003</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -3830,6 +4021,11 @@
       <c r="P39" t="n">
         <v>-70.775121</v>
       </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2163256193</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -3902,6 +4098,11 @@
       <c r="P40" t="n">
         <v>-70.77511</v>
       </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2163054369</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -3972,6 +4173,11 @@
       <c r="P41" t="n">
         <v>-70.60665400000001</v>
       </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2162859622</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -4042,6 +4248,11 @@
       <c r="P42" t="n">
         <v>-70.067031</v>
       </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2162611409</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -4114,6 +4325,11 @@
       <c r="P43" t="n">
         <v>-70.293525</v>
       </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2162453967</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -4186,6 +4402,11 @@
       <c r="P44" t="n">
         <v>-70.35227399999999</v>
       </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2162114269</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -4258,6 +4479,11 @@
       <c r="P45" t="n">
         <v>-70.832865</v>
       </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2162173616</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -4330,6 +4556,11 @@
       <c r="P46" t="n">
         <v>-71.248867</v>
       </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2162046386</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -4402,6 +4633,11 @@
       <c r="P47" t="n">
         <v>-69.270911</v>
       </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2161708542</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -4474,6 +4710,11 @@
       <c r="P48" t="n">
         <v>-69.876603</v>
       </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2161820386</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -4546,6 +4787,11 @@
       <c r="P49" t="n">
         <v>-71.23445</v>
       </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2161054052</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -4616,6 +4862,11 @@
       <c r="P50" t="n">
         <v>-70.000004</v>
       </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2161119773</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -4688,6 +4939,11 @@
       <c r="P51" t="n">
         <v>-70.261297</v>
       </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2160889496</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -4760,6 +5016,11 @@
       <c r="P52" t="n">
         <v>-70.247972</v>
       </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2160888328</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -4832,6 +5093,11 @@
       <c r="P53" t="n">
         <v>-70.77391900000001</v>
       </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2160922995</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -4904,6 +5170,11 @@
       <c r="P54" t="n">
         <v>-69.99999800000001</v>
       </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2160923507</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -4976,6 +5247,11 @@
       <c r="P55" t="n">
         <v>-70.817832</v>
       </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2160827417</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -5048,6 +5324,11 @@
       <c r="P56" t="n">
         <v>-70.226108</v>
       </c>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2160818896</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -5120,6 +5401,11 @@
       <c r="P57" t="n">
         <v>-70.028195</v>
       </c>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2160818870</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -5192,6 +5478,11 @@
       <c r="P58" t="n">
         <v>-70.06157899999999</v>
       </c>
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2160819403</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -5264,6 +5555,11 @@
       <c r="P59" t="n">
         <v>-70.06157899999999</v>
       </c>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2160825558</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -5336,6 +5632,11 @@
       <c r="P60" t="n">
         <v>-70.396558</v>
       </c>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2160823789</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -5408,6 +5709,11 @@
       <c r="P61" t="n">
         <v>-70.752505</v>
       </c>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2160552686</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -5480,6 +5786,11 @@
       <c r="P62" t="n">
         <v>-71</v>
       </c>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2160530909</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -5552,6 +5863,11 @@
       <c r="P63" t="n">
         <v>-70.254096</v>
       </c>
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2160547615</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -5624,6 +5940,11 @@
       <c r="P64" t="n">
         <v>-70.259737</v>
       </c>
+      <c r="Q64" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2160473045</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -5696,6 +6017,11 @@
       <c r="P65" t="n">
         <v>-70.002133</v>
       </c>
+      <c r="Q65" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2160291004</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -5768,6 +6094,11 @@
       <c r="P66" t="n">
         <v>-70.921772</v>
       </c>
+      <c r="Q66" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2160195363</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -5838,6 +6169,11 @@
       <c r="P67" t="n">
         <v>-70.70570600000001</v>
       </c>
+      <c r="Q67" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2160070851</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -5910,6 +6246,11 @@
       <c r="P68" t="n">
         <v>-70.044032</v>
       </c>
+      <c r="Q68" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2159799023</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -5982,6 +6323,11 @@
       <c r="P69" t="n">
         <v>-70.182885</v>
       </c>
+      <c r="Q69" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2159506661</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -6054,6 +6400,11 @@
       <c r="P70" t="n">
         <v>-71.089613</v>
       </c>
+      <c r="Q70" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2159345970</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -6126,6 +6477,11 @@
       <c r="P71" t="n">
         <v>-70.803766</v>
       </c>
+      <c r="Q71" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2159048502</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -6198,6 +6554,11 @@
       <c r="P72" t="n">
         <v>-70.981032</v>
       </c>
+      <c r="Q72" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2158698531</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -6270,6 +6631,11 @@
       <c r="P73" t="n">
         <v>-70.786106</v>
       </c>
+      <c r="Q73" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2158653115</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -6342,6 +6708,11 @@
       <c r="P74" t="n">
         <v>-69</v>
       </c>
+      <c r="Q74" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2158598281</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -6412,6 +6783,11 @@
       <c r="P75" t="n">
         <v>-70.79543623000001</v>
       </c>
+      <c r="Q75" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2158472615</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -6484,6 +6860,11 @@
       <c r="P76" t="n">
         <v>-70.913583</v>
       </c>
+      <c r="Q76" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2156946350</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -6556,6 +6937,11 @@
       <c r="P77" t="n">
         <v>-70.991544</v>
       </c>
+      <c r="Q77" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2155976017</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -6628,6 +7014,11 @@
       <c r="P78" t="n">
         <v>-70.350613</v>
       </c>
+      <c r="Q78" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2156200015</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -6700,6 +7091,11 @@
       <c r="P79" t="n">
         <v>-71.000005</v>
       </c>
+      <c r="Q79" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2155868894</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -6772,6 +7168,11 @@
       <c r="P80" t="n">
         <v>-70.924496</v>
       </c>
+      <c r="Q80" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2155656728</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -6844,6 +7245,11 @@
       <c r="P81" t="n">
         <v>-69.896917</v>
       </c>
+      <c r="Q81" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2155359327</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -6916,6 +7322,11 @@
       <c r="P82" t="n">
         <v>-70.30933</v>
       </c>
+      <c r="Q82" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2154637132</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -6988,6 +7399,11 @@
       <c r="P83" t="n">
         <v>-70.35929</v>
       </c>
+      <c r="Q83" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2154503680</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -7060,6 +7476,11 @@
       <c r="P84" t="n">
         <v>-69.608807</v>
       </c>
+      <c r="Q84" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2154403083</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -7132,6 +7553,11 @@
       <c r="P85" t="n">
         <v>-70.420743</v>
       </c>
+      <c r="Q85" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2154437881</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -7204,6 +7630,11 @@
       <c r="P86" t="n">
         <v>-69.837318</v>
       </c>
+      <c r="Q86" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2154450197</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -7276,6 +7707,11 @@
       <c r="P87" t="n">
         <v>-70.10414900000001</v>
       </c>
+      <c r="Q87" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2153950021</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -7348,6 +7784,11 @@
       <c r="P88" t="n">
         <v>-70.653043</v>
       </c>
+      <c r="Q88" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2153545252</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -7420,6 +7861,11 @@
       <c r="P89" t="n">
         <v>-70.814082</v>
       </c>
+      <c r="Q89" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2153540148</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -7492,6 +7938,11 @@
       <c r="P90" t="n">
         <v>-70.03895900000001</v>
       </c>
+      <c r="Q90" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2153072730</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -7564,6 +8015,11 @@
       <c r="P91" t="n">
         <v>-70.32452000000001</v>
       </c>
+      <c r="Q91" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2153083161</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -7636,6 +8092,11 @@
       <c r="P92" t="n">
         <v>-70.35315900000001</v>
       </c>
+      <c r="Q92" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2152997540</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -7706,6 +8167,11 @@
       <c r="P93" t="n">
         <v>-70.26679</v>
       </c>
+      <c r="Q93" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2153050412</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -7778,6 +8244,11 @@
       <c r="P94" t="n">
         <v>-70.544246</v>
       </c>
+      <c r="Q94" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2152750552</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -7850,6 +8321,11 @@
       <c r="P95" t="n">
         <v>-70.337228</v>
       </c>
+      <c r="Q95" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2152920279</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -7922,6 +8398,11 @@
       <c r="P96" t="n">
         <v>-70.760088</v>
       </c>
+      <c r="Q96" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2151773236</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -7994,6 +8475,11 @@
       <c r="P97" t="n">
         <v>-70.676844</v>
       </c>
+      <c r="Q97" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2151782381</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -8066,6 +8552,11 @@
       <c r="P98" t="n">
         <v>-70.754577</v>
       </c>
+      <c r="Q98" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2151787292</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -8138,6 +8629,11 @@
       <c r="P99" t="n">
         <v>-70.378467</v>
       </c>
+      <c r="Q99" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2152462382</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -8210,6 +8706,11 @@
       <c r="P100" t="n">
         <v>-70.379171</v>
       </c>
+      <c r="Q100" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2152179398</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -8282,6 +8783,11 @@
       <c r="P101" t="n">
         <v>-70.104894</v>
       </c>
+      <c r="Q101" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2152294730</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -8354,6 +8860,11 @@
       <c r="P102" t="n">
         <v>-69.320694</v>
       </c>
+      <c r="Q102" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2152041577</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -8426,6 +8937,11 @@
       <c r="P103" t="n">
         <v>-70.106076</v>
       </c>
+      <c r="Q103" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2151756224</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -8498,6 +9014,11 @@
       <c r="P104" t="n">
         <v>-70.106076</v>
       </c>
+      <c r="Q104" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2151796707</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -8570,6 +9091,11 @@
       <c r="P105" t="n">
         <v>-70.389584</v>
       </c>
+      <c r="Q105" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2151760182</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -8642,6 +9168,11 @@
       <c r="P106" t="n">
         <v>-70.106076</v>
       </c>
+      <c r="Q106" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2151504917</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -8714,6 +9245,11 @@
       <c r="P107" t="n">
         <v>-70.423743</v>
       </c>
+      <c r="Q107" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2151515602</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -8786,6 +9322,11 @@
       <c r="P108" t="n">
         <v>-70.406976</v>
       </c>
+      <c r="Q108" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2151531566</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -8858,6 +9399,11 @@
       <c r="P109" t="n">
         <v>-70.735792</v>
       </c>
+      <c r="Q109" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2151195059</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -8930,6 +9476,11 @@
       <c r="P110" t="n">
         <v>-70.266086</v>
       </c>
+      <c r="Q110" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2151199570</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -9002,6 +9553,11 @@
       <c r="P111" t="n">
         <v>-71.08494399999999</v>
       </c>
+      <c r="Q111" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2151199213</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -9074,6 +9630,11 @@
       <c r="P112" t="n">
         <v>-70.196073</v>
       </c>
+      <c r="Q112" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2151133881</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -9146,6 +9707,11 @@
       <c r="P113" t="n">
         <v>-70.72880000000001</v>
       </c>
+      <c r="Q113" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2150821143</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -9218,6 +9784,11 @@
       <c r="P114" t="n">
         <v>-70</v>
       </c>
+      <c r="Q114" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2150807737</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -9290,6 +9861,11 @@
       <c r="P115" t="n">
         <v>-70.067031</v>
       </c>
+      <c r="Q115" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2149722056</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -9362,6 +9938,11 @@
       <c r="P116" t="n">
         <v>-69</v>
       </c>
+      <c r="Q116" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2149498666</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -9434,6 +10015,11 @@
       <c r="P117" t="n">
         <v>-70.25470900000001</v>
       </c>
+      <c r="Q117" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2149456416</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -9506,6 +10092,11 @@
       <c r="P118" t="n">
         <v>-70.175068</v>
       </c>
+      <c r="Q118" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2149560764</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -9578,6 +10169,11 @@
       <c r="P119" t="n">
         <v>-70.604578</v>
       </c>
+      <c r="Q119" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2149415708</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -9650,6 +10246,11 @@
       <c r="P120" t="n">
         <v>-70.779438</v>
       </c>
+      <c r="Q120" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2149355192</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -9722,6 +10323,11 @@
       <c r="P121" t="n">
         <v>-70.274382</v>
       </c>
+      <c r="Q121" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2149212398</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -9794,6 +10400,11 @@
       <c r="P122" t="n">
         <v>-70.32222400000001</v>
       </c>
+      <c r="Q122" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2149269406</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -9864,6 +10475,11 @@
       <c r="P123" t="n">
         <v>-70.119849</v>
       </c>
+      <c r="Q123" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2147570450</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -9936,6 +10552,11 @@
       <c r="P124" t="n">
         <v>-71</v>
       </c>
+      <c r="Q124" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2149085864</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -10008,6 +10629,11 @@
       <c r="P125" t="n">
         <v>-70.033171</v>
       </c>
+      <c r="Q125" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2148728101</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -10080,6 +10706,11 @@
       <c r="P126" t="n">
         <v>-70.45201</v>
       </c>
+      <c r="Q126" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2148859662</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -10152,6 +10783,11 @@
       <c r="P127" t="n">
         <v>-70.322889</v>
       </c>
+      <c r="Q127" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2148693376</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -10224,6 +10860,11 @@
       <c r="P128" t="n">
         <v>-71.00730299999999</v>
       </c>
+      <c r="Q128" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2148047522</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -10296,6 +10937,11 @@
       <c r="P129" t="n">
         <v>-71</v>
       </c>
+      <c r="Q129" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2147543739</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -10368,6 +11014,11 @@
       <c r="P130" t="n">
         <v>-70.01775000000001</v>
       </c>
+      <c r="Q130" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2147449385</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -10440,6 +11091,11 @@
       <c r="P131" t="n">
         <v>-70.71287700000001</v>
       </c>
+      <c r="Q131" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2147480787</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -10512,6 +11168,11 @@
       <c r="P132" t="n">
         <v>-70.689922</v>
       </c>
+      <c r="Q132" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2146732431</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -10584,6 +11245,11 @@
       <c r="P133" t="n">
         <v>-70.041602</v>
       </c>
+      <c r="Q133" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2146824378</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -10656,6 +11322,11 @@
       <c r="P134" t="n">
         <v>-69.99999699999999</v>
       </c>
+      <c r="Q134" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2146717942</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -10728,6 +11399,11 @@
       <c r="P135" t="n">
         <v>-70.19812899999999</v>
       </c>
+      <c r="Q135" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2146438896</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -10800,6 +11476,11 @@
       <c r="P136" t="n">
         <v>-69.320679</v>
       </c>
+      <c r="Q136" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2146327399</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -10872,6 +11553,11 @@
       <c r="P137" t="n">
         <v>-70.459149</v>
       </c>
+      <c r="Q137" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2146303924</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -10944,6 +11630,11 @@
       <c r="P138" t="n">
         <v>-71.47555800000001</v>
       </c>
+      <c r="Q138" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2145215136</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -11016,6 +11707,11 @@
       <c r="P139" t="n">
         <v>-70.40946599999999</v>
       </c>
+      <c r="Q139" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2146359939</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -11088,6 +11784,11 @@
       <c r="P140" t="n">
         <v>-70.4089</v>
       </c>
+      <c r="Q140" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2146341366</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -11160,6 +11861,11 @@
       <c r="P141" t="n">
         <v>-70.26974199999999</v>
       </c>
+      <c r="Q141" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2146027911</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -11232,6 +11938,11 @@
       <c r="P142" t="n">
         <v>-70.269587</v>
       </c>
+      <c r="Q142" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2146014553</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -11304,6 +12015,11 @@
       <c r="P143" t="n">
         <v>-70.73356200000001</v>
       </c>
+      <c r="Q143" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2145974457</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -11376,6 +12092,11 @@
       <c r="P144" t="n">
         <v>-70.31918400000001</v>
       </c>
+      <c r="Q144" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2145959433</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -11448,6 +12169,11 @@
       <c r="P145" t="n">
         <v>-70.383425</v>
       </c>
+      <c r="Q145" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2145974445</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -11520,6 +12246,11 @@
       <c r="P146" t="n">
         <v>-70.331632</v>
       </c>
+      <c r="Q146" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2145805604</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -11592,6 +12323,11 @@
       <c r="P147" t="n">
         <v>-71.23494599999999</v>
       </c>
+      <c r="Q147" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2145744315</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -11664,6 +12400,11 @@
       <c r="P148" t="n">
         <v>-70.91624400000001</v>
       </c>
+      <c r="Q148" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2145736955</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -11736,6 +12477,11 @@
       <c r="P149" t="n">
         <v>-70.36080800000001</v>
       </c>
+      <c r="Q149" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2145755946</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -11808,6 +12554,11 @@
       <c r="P150" t="n">
         <v>-69.036581</v>
       </c>
+      <c r="Q150" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2145562036</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -11880,6 +12631,11 @@
       <c r="P151" t="n">
         <v>-71</v>
       </c>
+      <c r="Q151" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2145368256</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -11952,6 +12708,11 @@
       <c r="P152" t="n">
         <v>-69.84128</v>
       </c>
+      <c r="Q152" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2145382610</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -12024,6 +12785,11 @@
       <c r="P153" t="n">
         <v>-70.816692</v>
       </c>
+      <c r="Q153" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2145025525</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -12096,6 +12862,11 @@
       <c r="P154" t="n">
         <v>-70.194076</v>
       </c>
+      <c r="Q154" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2145240384</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -12168,6 +12939,11 @@
       <c r="P155" t="n">
         <v>-70.321153</v>
       </c>
+      <c r="Q155" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2144258848</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -12240,6 +13016,11 @@
       <c r="P156" t="n">
         <v>-69.99999800000001</v>
       </c>
+      <c r="Q156" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2144203593</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -12312,6 +13093,11 @@
       <c r="P157" t="n">
         <v>-70.365938</v>
       </c>
+      <c r="Q157" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2144294779</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -12384,6 +13170,11 @@
       <c r="P158" t="n">
         <v>-70.76080899999999</v>
       </c>
+      <c r="Q158" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2144259989</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -12456,6 +13247,11 @@
       <c r="P159" t="n">
         <v>-70.110101</v>
       </c>
+      <c r="Q159" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2144135731</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -12528,6 +13324,11 @@
       <c r="P160" t="n">
         <v>-70.122856</v>
       </c>
+      <c r="Q160" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2144204940</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -12600,6 +13401,11 @@
       <c r="P161" t="n">
         <v>-70.254499</v>
       </c>
+      <c r="Q161" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2144075499</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -12672,6 +13478,11 @@
       <c r="P162" t="n">
         <v>-69.30321600000001</v>
       </c>
+      <c r="Q162" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2143861974</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -12744,6 +13555,11 @@
       <c r="P163" t="n">
         <v>-70.06314999999999</v>
       </c>
+      <c r="Q163" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2143533013</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -12816,6 +13632,11 @@
       <c r="P164" t="n">
         <v>-71.212182</v>
       </c>
+      <c r="Q164" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2143239045</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -12888,6 +13709,11 @@
       <c r="P165" t="n">
         <v>-71.25784400000001</v>
       </c>
+      <c r="Q165" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2143239139</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -12960,6 +13786,11 @@
       <c r="P166" t="n">
         <v>-70.00000199999999</v>
       </c>
+      <c r="Q166" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2143271078</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -13032,6 +13863,11 @@
       <c r="P167" t="n">
         <v>-70.893674</v>
       </c>
+      <c r="Q167" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2143174680</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -13104,6 +13940,11 @@
       <c r="P168" t="n">
         <v>-69.243697</v>
       </c>
+      <c r="Q168" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2143054220</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -13176,6 +14017,11 @@
       <c r="P169" t="n">
         <v>-70.738839</v>
       </c>
+      <c r="Q169" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2142138303</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -13248,6 +14094,11 @@
       <c r="P170" t="n">
         <v>-70.895556</v>
       </c>
+      <c r="Q170" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2142158280</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -13320,6 +14171,11 @@
       <c r="P171" t="n">
         <v>-68.978573</v>
       </c>
+      <c r="Q171" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2142117538</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -13392,6 +14248,11 @@
       <c r="P172" t="n">
         <v>-69.918841</v>
       </c>
+      <c r="Q172" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2141955132</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -13464,6 +14325,11 @@
       <c r="P173" t="n">
         <v>-70.28429300000001</v>
       </c>
+      <c r="Q173" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2142073809</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -13536,6 +14402,11 @@
       <c r="P174" t="n">
         <v>-71.493171</v>
       </c>
+      <c r="Q174" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2141864338</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -13608,6 +14479,11 @@
       <c r="P175" t="n">
         <v>-70.654087</v>
       </c>
+      <c r="Q175" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2141608785</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -13680,6 +14556,11 @@
       <c r="P176" t="n">
         <v>-69.61119100000001</v>
       </c>
+      <c r="Q176" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2141618022</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -13752,6 +14633,11 @@
       <c r="P177" t="n">
         <v>-71.24709</v>
       </c>
+      <c r="Q177" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2141484534</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -13824,6 +14710,11 @@
       <c r="P178" t="n">
         <v>-69.975126</v>
       </c>
+      <c r="Q178" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2141406582</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -13896,6 +14787,11 @@
       <c r="P179" t="n">
         <v>-69.091381</v>
       </c>
+      <c r="Q179" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2141400811</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -13968,6 +14864,11 @@
       <c r="P180" t="n">
         <v>-70.38294</v>
       </c>
+      <c r="Q180" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2141395212</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -14040,6 +14941,11 @@
       <c r="P181" t="n">
         <v>-71.398394</v>
       </c>
+      <c r="Q181" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2141393316</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -14112,6 +15018,11 @@
       <c r="P182" t="n">
         <v>-70.884829</v>
       </c>
+      <c r="Q182" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2141395159</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -14184,6 +15095,11 @@
       <c r="P183" t="n">
         <v>-69.684651</v>
       </c>
+      <c r="Q183" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2141049369</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -14256,6 +15172,11 @@
       <c r="P184" t="n">
         <v>-70.16182000000001</v>
       </c>
+      <c r="Q184" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2141176364</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -14328,6 +15249,11 @@
       <c r="P185" t="n">
         <v>-70.310813</v>
       </c>
+      <c r="Q185" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2141216594</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -14400,6 +15326,11 @@
       <c r="P186" t="n">
         <v>-70.32880900000001</v>
       </c>
+      <c r="Q186" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2141062692</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -14472,6 +15403,11 @@
       <c r="P187" t="n">
         <v>-70.535115</v>
       </c>
+      <c r="Q187" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2141009799</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -14544,6 +15480,11 @@
       <c r="P188" t="n">
         <v>-68.908134</v>
       </c>
+      <c r="Q188" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2140923517</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -14616,6 +15557,11 @@
       <c r="P189" t="n">
         <v>-69.121565</v>
       </c>
+      <c r="Q189" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2140882659</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -14688,6 +15634,11 @@
       <c r="P190" t="n">
         <v>-71.247941</v>
       </c>
+      <c r="Q190" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2139226316</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -14760,6 +15711,11 @@
       <c r="P191" t="n">
         <v>-70.037209</v>
       </c>
+      <c r="Q191" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2139190135</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -14832,6 +15788,11 @@
       <c r="P192" t="n">
         <v>-69.47774200000001</v>
       </c>
+      <c r="Q192" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2138993240</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -14904,6 +15865,11 @@
       <c r="P193" t="n">
         <v>-70.804796</v>
       </c>
+      <c r="Q193" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2138417150</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -14976,6 +15942,11 @@
       <c r="P194" t="n">
         <v>-71.254239</v>
       </c>
+      <c r="Q194" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2138239993</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -15048,6 +16019,11 @@
       <c r="P195" t="n">
         <v>-70.272018</v>
       </c>
+      <c r="Q195" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2138007308</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -15120,6 +16096,11 @@
       <c r="P196" t="n">
         <v>-70.784425</v>
       </c>
+      <c r="Q196" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2135212788</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -15192,6 +16173,11 @@
       <c r="P197" t="n">
         <v>-70.92133200000001</v>
       </c>
+      <c r="Q197" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2132734337</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -15264,6 +16250,11 @@
       <c r="P198" t="n">
         <v>-70.10780699999999</v>
       </c>
+      <c r="Q198" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2132653321</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -15336,6 +16327,11 @@
       <c r="P199" t="n">
         <v>-70.919398</v>
       </c>
+      <c r="Q199" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2132574597</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -15408,6 +16404,11 @@
       <c r="P200" t="n">
         <v>-70.009398</v>
       </c>
+      <c r="Q200" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2132568141</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -15480,6 +16481,11 @@
       <c r="P201" t="n">
         <v>-70.228632</v>
       </c>
+      <c r="Q201" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2132555985</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -15552,6 +16558,11 @@
       <c r="P202" t="n">
         <v>-70.630296</v>
       </c>
+      <c r="Q202" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2132536275</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -15624,6 +16635,11 @@
       <c r="P203" t="n">
         <v>-70.819599</v>
       </c>
+      <c r="Q203" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2132370783</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -15696,6 +16712,11 @@
       <c r="P204" t="n">
         <v>-70.197802</v>
       </c>
+      <c r="Q204" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2132391105</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -15768,6 +16789,11 @@
       <c r="P205" t="n">
         <v>-70.27437399999999</v>
       </c>
+      <c r="Q205" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2132353194</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -15840,6 +16866,11 @@
       <c r="P206" t="n">
         <v>-70.621838</v>
       </c>
+      <c r="Q206" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2132374108</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -15912,6 +16943,11 @@
       <c r="P207" t="n">
         <v>-70.40297700000001</v>
       </c>
+      <c r="Q207" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2132353120</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -15984,6 +17020,11 @@
       <c r="P208" t="n">
         <v>-70.242327</v>
       </c>
+      <c r="Q208" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2132335053</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -16056,6 +17097,11 @@
       <c r="P209" t="n">
         <v>-71.475075</v>
       </c>
+      <c r="Q209" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2132282084</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -16128,6 +17174,11 @@
       <c r="P210" t="n">
         <v>-70.808362</v>
       </c>
+      <c r="Q210" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2132259238</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -16200,6 +17251,11 @@
       <c r="P211" t="n">
         <v>-70.32808799999999</v>
       </c>
+      <c r="Q211" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2132151354</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -16272,6 +17328,11 @@
       <c r="P212" t="n">
         <v>-70.24654700000001</v>
       </c>
+      <c r="Q212" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2132072866</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -16344,6 +17405,11 @@
       <c r="P213" t="n">
         <v>-70.272558</v>
       </c>
+      <c r="Q213" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2132040105</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -16416,6 +17482,11 @@
       <c r="P214" t="n">
         <v>-71.023352</v>
       </c>
+      <c r="Q214" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2131912425</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -16488,6 +17559,11 @@
       <c r="P215" t="n">
         <v>-70.816515</v>
       </c>
+      <c r="Q215" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2131946197</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -16560,6 +17636,11 @@
       <c r="P216" t="n">
         <v>-70.25293000000001</v>
       </c>
+      <c r="Q216" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2131886963</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -16632,6 +17713,11 @@
       <c r="P217" t="n">
         <v>-69.587101</v>
       </c>
+      <c r="Q217" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2131844878</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -16704,6 +17790,11 @@
       <c r="P218" t="n">
         <v>-69.94967</v>
       </c>
+      <c r="Q218" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2131753914</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -16776,6 +17867,11 @@
       <c r="P219" t="n">
         <v>-70.78693</v>
       </c>
+      <c r="Q219" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2131714991</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -16848,6 +17944,11 @@
       <c r="P220" t="n">
         <v>-71.25656600000001</v>
       </c>
+      <c r="Q220" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2131701502</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -16920,6 +18021,11 @@
       <c r="P221" t="n">
         <v>-69.828057</v>
       </c>
+      <c r="Q221" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2131691169</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -16992,6 +18098,11 @@
       <c r="P222" t="n">
         <v>-70.74772</v>
       </c>
+      <c r="Q222" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2131618584</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -17064,6 +18175,11 @@
       <c r="P223" t="n">
         <v>-70.791197</v>
       </c>
+      <c r="Q223" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2131608224</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -17136,6 +18252,11 @@
       <c r="P224" t="n">
         <v>-70.98291399999999</v>
       </c>
+      <c r="Q224" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2131608822</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -17208,6 +18329,11 @@
       <c r="P225" t="n">
         <v>-70.89097700000001</v>
       </c>
+      <c r="Q225" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2131542392</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -17280,6 +18406,11 @@
       <c r="P226" t="n">
         <v>-70.126643</v>
       </c>
+      <c r="Q226" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2131504161</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -17352,6 +18483,11 @@
       <c r="P227" t="n">
         <v>-70.893985</v>
       </c>
+      <c r="Q227" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2131352879</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -17424,6 +18560,11 @@
       <c r="P228" t="n">
         <v>-69.90384899999999</v>
       </c>
+      <c r="Q228" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2131325249</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -17496,6 +18637,11 @@
       <c r="P229" t="n">
         <v>-70.328025</v>
       </c>
+      <c r="Q229" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2131319797</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -17568,6 +18714,11 @@
       <c r="P230" t="n">
         <v>-70.86417899999999</v>
       </c>
+      <c r="Q230" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2131303248</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -17640,6 +18791,11 @@
       <c r="P231" t="n">
         <v>-69.60139700000001</v>
       </c>
+      <c r="Q231" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2131240405</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -17712,6 +18868,11 @@
       <c r="P232" t="n">
         <v>-70.093225</v>
       </c>
+      <c r="Q232" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2131264105</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -17784,6 +18945,11 @@
       <c r="P233" t="n">
         <v>-70.91908100000001</v>
       </c>
+      <c r="Q233" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2131204000</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -17856,6 +19022,11 @@
       <c r="P234" t="n">
         <v>-69.920007</v>
       </c>
+      <c r="Q234" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2131186928</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -17928,6 +19099,11 @@
       <c r="P235" t="n">
         <v>-69.93061899999999</v>
       </c>
+      <c r="Q235" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2131186903</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -18000,6 +19176,11 @@
       <c r="P236" t="n">
         <v>-70.077153</v>
       </c>
+      <c r="Q236" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2131184390</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -18072,6 +19253,11 @@
       <c r="P237" t="n">
         <v>-69.96079400000001</v>
       </c>
+      <c r="Q237" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2131186866</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -18144,6 +19330,11 @@
       <c r="P238" t="n">
         <v>-69.958962</v>
       </c>
+      <c r="Q238" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2131186840</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -18216,6 +19407,11 @@
       <c r="P239" t="n">
         <v>-69.901892</v>
       </c>
+      <c r="Q239" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2131185357</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -18288,6 +19484,11 @@
       <c r="P240" t="n">
         <v>-69.96014700000001</v>
       </c>
+      <c r="Q240" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2131180805</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -18360,6 +19561,11 @@
       <c r="P241" t="n">
         <v>-70.810193</v>
       </c>
+      <c r="Q241" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2131139998</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -18432,6 +19638,11 @@
       <c r="P242" t="n">
         <v>-68.9118</v>
       </c>
+      <c r="Q242" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2131114614</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -18504,6 +19715,11 @@
       <c r="P243" t="n">
         <v>-69.91287800000001</v>
       </c>
+      <c r="Q243" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2131099448</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -18576,6 +19792,11 @@
       <c r="P244" t="n">
         <v>-70.37549300000001</v>
       </c>
+      <c r="Q244" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2131096688</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -18648,6 +19869,11 @@
       <c r="P245" t="n">
         <v>-70.316913</v>
       </c>
+      <c r="Q245" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2131026061</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -18720,6 +19946,11 @@
       <c r="P246" t="n">
         <v>-70.814094</v>
       </c>
+      <c r="Q246" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2130978325</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -18792,6 +20023,11 @@
       <c r="P247" t="n">
         <v>-70.638943</v>
       </c>
+      <c r="Q247" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2131015138</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -18864,6 +20100,11 @@
       <c r="P248" t="n">
         <v>-70.91627699999999</v>
       </c>
+      <c r="Q248" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2130999109</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -18936,6 +20177,11 @@
       <c r="P249" t="n">
         <v>-70.26632600000001</v>
       </c>
+      <c r="Q249" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2130936751</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -19008,6 +20254,11 @@
       <c r="P250" t="n">
         <v>-70.157247</v>
       </c>
+      <c r="Q250" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2130903114</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -19080,6 +20331,11 @@
       <c r="P251" t="n">
         <v>-69.23986499999999</v>
       </c>
+      <c r="Q251" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2130902047</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -19152,6 +20408,11 @@
       <c r="P252" t="n">
         <v>-71.04418699999999</v>
       </c>
+      <c r="Q252" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2130892867</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -19224,6 +20485,11 @@
       <c r="P253" t="n">
         <v>-70.314598</v>
       </c>
+      <c r="Q253" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2130794609</t>
+        </is>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -19296,6 +20562,11 @@
       <c r="P254" t="n">
         <v>-69.936661</v>
       </c>
+      <c r="Q254" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2130745613</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -19368,6 +20639,11 @@
       <c r="P255" t="n">
         <v>-69.78815</v>
       </c>
+      <c r="Q255" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2130785742</t>
+        </is>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -19440,6 +20716,11 @@
       <c r="P256" t="n">
         <v>-70.328119</v>
       </c>
+      <c r="Q256" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2130753835</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -19512,6 +20793,11 @@
       <c r="P257" t="n">
         <v>-70.389065</v>
       </c>
+      <c r="Q257" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2130705679</t>
+        </is>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -19584,6 +20870,11 @@
       <c r="P258" t="n">
         <v>-69.968782</v>
       </c>
+      <c r="Q258" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2130712389</t>
+        </is>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -19656,6 +20947,11 @@
       <c r="P259" t="n">
         <v>-70.67909899999999</v>
       </c>
+      <c r="Q259" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2130669594</t>
+        </is>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
@@ -19728,6 +21024,11 @@
       <c r="P260" t="n">
         <v>-70.814514</v>
       </c>
+      <c r="Q260" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2130644164</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -19800,6 +21101,11 @@
       <c r="P261" t="n">
         <v>-69.24341</v>
       </c>
+      <c r="Q261" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2130621178</t>
+        </is>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
@@ -19872,6 +21178,11 @@
       <c r="P262" t="n">
         <v>-71.067949</v>
       </c>
+      <c r="Q262" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2130592087</t>
+        </is>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -19944,6 +21255,11 @@
       <c r="P263" t="n">
         <v>-70.42346999999999</v>
       </c>
+      <c r="Q263" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2130564655</t>
+        </is>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
@@ -20016,6 +21332,11 @@
       <c r="P264" t="n">
         <v>-70.89072</v>
       </c>
+      <c r="Q264" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2130547382</t>
+        </is>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
@@ -20088,6 +21409,11 @@
       <c r="P265" t="n">
         <v>-70.713802</v>
       </c>
+      <c r="Q265" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2130493442</t>
+        </is>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
@@ -20160,6 +21486,11 @@
       <c r="P266" t="n">
         <v>-69.919263</v>
       </c>
+      <c r="Q266" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2130474405</t>
+        </is>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
@@ -20232,6 +21563,11 @@
       <c r="P267" t="n">
         <v>-70.915963</v>
       </c>
+      <c r="Q267" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2130321412</t>
+        </is>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
@@ -20304,6 +21640,11 @@
       <c r="P268" t="n">
         <v>-69.877161</v>
       </c>
+      <c r="Q268" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2130221015</t>
+        </is>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
@@ -20376,6 +21717,11 @@
       <c r="P269" t="n">
         <v>-69.887788</v>
       </c>
+      <c r="Q269" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2130240342</t>
+        </is>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
@@ -20448,6 +21794,11 @@
       <c r="P270" t="n">
         <v>-70.38706999999999</v>
       </c>
+      <c r="Q270" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2130251345</t>
+        </is>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -20520,6 +21871,11 @@
       <c r="P271" t="n">
         <v>-70.396506</v>
       </c>
+      <c r="Q271" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2130251383</t>
+        </is>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
@@ -20592,6 +21948,11 @@
       <c r="P272" t="n">
         <v>-70.180941</v>
       </c>
+      <c r="Q272" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2130251113</t>
+        </is>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
@@ -20664,6 +22025,11 @@
       <c r="P273" t="n">
         <v>-70.210127</v>
       </c>
+      <c r="Q273" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2130250395</t>
+        </is>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
@@ -20736,6 +22102,11 @@
       <c r="P274" t="n">
         <v>-69.98728699999999</v>
       </c>
+      <c r="Q274" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2130154798</t>
+        </is>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
@@ -20808,6 +22179,11 @@
       <c r="P275" t="n">
         <v>-70.39778</v>
       </c>
+      <c r="Q275" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2130108890</t>
+        </is>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
@@ -20880,6 +22256,11 @@
       <c r="P276" t="n">
         <v>-70.889994</v>
       </c>
+      <c r="Q276" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2130076799</t>
+        </is>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
@@ -20952,6 +22333,11 @@
       <c r="P277" t="n">
         <v>-70.84953899999999</v>
       </c>
+      <c r="Q277" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2130018791</t>
+        </is>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
@@ -21024,6 +22410,11 @@
       <c r="P278" t="n">
         <v>-70.769925</v>
       </c>
+      <c r="Q278" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2130018046</t>
+        </is>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
@@ -21096,6 +22487,11 @@
       <c r="P279" t="n">
         <v>-70.388775</v>
       </c>
+      <c r="Q279" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2129961531</t>
+        </is>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
@@ -21168,6 +22564,11 @@
       <c r="P280" t="n">
         <v>-69.943099</v>
       </c>
+      <c r="Q280" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2129919147</t>
+        </is>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
@@ -21240,6 +22641,11 @@
       <c r="P281" t="n">
         <v>-69.923388</v>
       </c>
+      <c r="Q281" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2129919791</t>
+        </is>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
@@ -21312,6 +22718,11 @@
       <c r="P282" t="n">
         <v>-70.924758</v>
       </c>
+      <c r="Q282" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2129927663</t>
+        </is>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
@@ -21384,6 +22795,11 @@
       <c r="P283" t="n">
         <v>-70.641987</v>
       </c>
+      <c r="Q283" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2129966744</t>
+        </is>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
@@ -21456,6 +22872,11 @@
       <c r="P284" t="n">
         <v>-70.26702899999999</v>
       </c>
+      <c r="Q284" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2129960379</t>
+        </is>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
@@ -21528,6 +22949,11 @@
       <c r="P285" t="n">
         <v>-69.831025</v>
       </c>
+      <c r="Q285" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2129864122</t>
+        </is>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
@@ -21600,6 +23026,11 @@
       <c r="P286" t="n">
         <v>-70.431044</v>
       </c>
+      <c r="Q286" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2129817245</t>
+        </is>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
@@ -21672,6 +23103,11 @@
       <c r="P287" t="n">
         <v>-70.696943</v>
       </c>
+      <c r="Q287" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2129630686</t>
+        </is>
+      </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
@@ -21744,6 +23180,11 @@
       <c r="P288" t="n">
         <v>-71.253651</v>
       </c>
+      <c r="Q288" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2129636970</t>
+        </is>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
@@ -21816,6 +23257,11 @@
       <c r="P289" t="n">
         <v>-70.220276</v>
       </c>
+      <c r="Q289" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2129490663</t>
+        </is>
+      </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
@@ -21888,6 +23334,11 @@
       <c r="P290" t="n">
         <v>-69.98895899999999</v>
       </c>
+      <c r="Q290" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2129452450</t>
+        </is>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
@@ -21960,6 +23411,11 @@
       <c r="P291" t="n">
         <v>-69.70707299999999</v>
       </c>
+      <c r="Q291" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2129481834</t>
+        </is>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
@@ -22032,6 +23488,11 @@
       <c r="P292" t="n">
         <v>-70.09152899999999</v>
       </c>
+      <c r="Q292" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2129409487</t>
+        </is>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
@@ -22104,6 +23565,11 @@
       <c r="P293" t="n">
         <v>-70.226634</v>
       </c>
+      <c r="Q293" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2129356323</t>
+        </is>
+      </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
@@ -22176,6 +23642,11 @@
       <c r="P294" t="n">
         <v>-70.395403</v>
       </c>
+      <c r="Q294" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2128963662</t>
+        </is>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
@@ -22248,6 +23719,11 @@
       <c r="P295" t="n">
         <v>-69.947829</v>
       </c>
+      <c r="Q295" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2128970235</t>
+        </is>
+      </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
@@ -22320,6 +23796,11 @@
       <c r="P296" t="n">
         <v>-69.936199</v>
       </c>
+      <c r="Q296" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2128971400</t>
+        </is>
+      </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
@@ -22392,6 +23873,11 @@
       <c r="P297" t="n">
         <v>-70.110985</v>
       </c>
+      <c r="Q297" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2128975733</t>
+        </is>
+      </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
@@ -22464,6 +23950,11 @@
       <c r="P298" t="n">
         <v>-70.922861</v>
       </c>
+      <c r="Q298" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2128949909</t>
+        </is>
+      </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
@@ -22536,6 +24027,11 @@
       <c r="P299" t="n">
         <v>-69.907214</v>
       </c>
+      <c r="Q299" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2128950063</t>
+        </is>
+      </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
@@ -22608,6 +24104,11 @@
       <c r="P300" t="n">
         <v>-69.87292100000001</v>
       </c>
+      <c r="Q300" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2128950673</t>
+        </is>
+      </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
@@ -22680,6 +24181,11 @@
       <c r="P301" t="n">
         <v>-69.895861</v>
       </c>
+      <c r="Q301" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2128954737</t>
+        </is>
+      </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
@@ -22752,6 +24258,11 @@
       <c r="P302" t="n">
         <v>-70.806398</v>
       </c>
+      <c r="Q302" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2128956275</t>
+        </is>
+      </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
@@ -22824,6 +24335,11 @@
       <c r="P303" t="n">
         <v>-70.199326</v>
       </c>
+      <c r="Q303" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2128959854</t>
+        </is>
+      </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
@@ -22896,6 +24412,11 @@
       <c r="P304" t="n">
         <v>-70.448049</v>
       </c>
+      <c r="Q304" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2128896561</t>
+        </is>
+      </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
@@ -22968,6 +24489,11 @@
       <c r="P305" t="n">
         <v>-69.940405</v>
       </c>
+      <c r="Q305" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2128916297</t>
+        </is>
+      </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
@@ -23040,6 +24566,11 @@
       <c r="P306" t="n">
         <v>-69.943721</v>
       </c>
+      <c r="Q306" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2128913107</t>
+        </is>
+      </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
@@ -23112,6 +24643,11 @@
       <c r="P307" t="n">
         <v>-70.806568</v>
       </c>
+      <c r="Q307" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2128887244</t>
+        </is>
+      </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
@@ -23184,6 +24720,11 @@
       <c r="P308" t="n">
         <v>-70.69246699999999</v>
       </c>
+      <c r="Q308" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2128889920</t>
+        </is>
+      </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
@@ -23256,6 +24797,11 @@
       <c r="P309" t="n">
         <v>-70.744885</v>
       </c>
+      <c r="Q309" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2128855769</t>
+        </is>
+      </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
@@ -23328,6 +24874,11 @@
       <c r="P310" t="n">
         <v>-69.942374</v>
       </c>
+      <c r="Q310" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2128854659</t>
+        </is>
+      </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
@@ -23400,6 +24951,11 @@
       <c r="P311" t="n">
         <v>-70.696943</v>
       </c>
+      <c r="Q311" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2128863542</t>
+        </is>
+      </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
@@ -23472,6 +25028,11 @@
       <c r="P312" t="n">
         <v>-69.935501</v>
       </c>
+      <c r="Q312" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2128806555</t>
+        </is>
+      </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
@@ -23544,6 +25105,11 @@
       <c r="P313" t="n">
         <v>-71.233728</v>
       </c>
+      <c r="Q313" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2128712555</t>
+        </is>
+      </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
@@ -23616,6 +25182,11 @@
       <c r="P314" t="n">
         <v>-70.267957</v>
       </c>
+      <c r="Q314" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2128795612</t>
+        </is>
+      </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
@@ -23688,6 +25259,11 @@
       <c r="P315" t="n">
         <v>-70.606319</v>
       </c>
+      <c r="Q315" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2128797407</t>
+        </is>
+      </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
@@ -23760,6 +25336,11 @@
       <c r="P316" t="n">
         <v>-69.577384</v>
       </c>
+      <c r="Q316" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2128798084</t>
+        </is>
+      </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
@@ -23832,6 +25413,11 @@
       <c r="P317" t="n">
         <v>-70.058447</v>
       </c>
+      <c r="Q317" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2128792719</t>
+        </is>
+      </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
@@ -23904,6 +25490,11 @@
       <c r="P318" t="n">
         <v>-70.912049</v>
       </c>
+      <c r="Q318" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2128786911</t>
+        </is>
+      </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
@@ -23976,6 +25567,11 @@
       <c r="P319" t="n">
         <v>-70.213385</v>
       </c>
+      <c r="Q319" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2128768491</t>
+        </is>
+      </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
@@ -24048,6 +25644,11 @@
       <c r="P320" t="n">
         <v>-70.00297</v>
       </c>
+      <c r="Q320" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2128721265</t>
+        </is>
+      </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
@@ -24120,6 +25721,11 @@
       <c r="P321" t="n">
         <v>-70.27391299999999</v>
       </c>
+      <c r="Q321" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2128735932</t>
+        </is>
+      </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
@@ -24192,6 +25798,11 @@
       <c r="P322" t="n">
         <v>-69.922268</v>
       </c>
+      <c r="Q322" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2128718148</t>
+        </is>
+      </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
@@ -24264,6 +25875,11 @@
       <c r="P323" t="n">
         <v>-69.96002900000001</v>
       </c>
+      <c r="Q323" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2128701581</t>
+        </is>
+      </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
@@ -24336,6 +25952,11 @@
       <c r="P324" t="n">
         <v>-70.817561</v>
       </c>
+      <c r="Q324" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2128662037</t>
+        </is>
+      </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
@@ -24408,6 +26029,11 @@
       <c r="P325" t="n">
         <v>-70.03218099999999</v>
       </c>
+      <c r="Q325" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2128657104</t>
+        </is>
+      </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
@@ -24480,6 +26106,11 @@
       <c r="P326" t="n">
         <v>-70.836692</v>
       </c>
+      <c r="Q326" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2128621520</t>
+        </is>
+      </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
@@ -24552,6 +26183,11 @@
       <c r="P327" t="n">
         <v>-70.18912400000001</v>
       </c>
+      <c r="Q327" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2128586784</t>
+        </is>
+      </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
@@ -24624,6 +26260,11 @@
       <c r="P328" t="n">
         <v>-70.3032</v>
       </c>
+      <c r="Q328" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2128574336</t>
+        </is>
+      </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
@@ -24696,6 +26337,11 @@
       <c r="P329" t="n">
         <v>-70.267645</v>
       </c>
+      <c r="Q329" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2128540673</t>
+        </is>
+      </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
@@ -24768,6 +26414,11 @@
       <c r="P330" t="n">
         <v>-69.284851</v>
       </c>
+      <c r="Q330" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2128508976</t>
+        </is>
+      </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
@@ -24840,6 +26491,11 @@
       <c r="P331" t="n">
         <v>-70.826346</v>
       </c>
+      <c r="Q331" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=2128496962</t>
+        </is>
+      </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
@@ -24912,6 +26568,11 @@
       <c r="P332" t="n">
         <v>-70.17335199999999</v>
       </c>
+      <c r="Q332" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=8384389</t>
+        </is>
+      </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
@@ -24984,6 +26645,11 @@
       <c r="P333" t="n">
         <v>-70.18434600000001</v>
       </c>
+      <c r="Q333" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=8377764</t>
+        </is>
+      </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
@@ -25056,6 +26722,11 @@
       <c r="P334" t="n">
         <v>-70.388775</v>
       </c>
+      <c r="Q334" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=8361870</t>
+        </is>
+      </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
@@ -25128,6 +26799,11 @@
       <c r="P335" t="n">
         <v>-69.898605</v>
       </c>
+      <c r="Q335" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=8351504</t>
+        </is>
+      </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
@@ -25200,6 +26876,11 @@
       <c r="P336" t="n">
         <v>-69.608667</v>
       </c>
+      <c r="Q336" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=8344686</t>
+        </is>
+      </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
@@ -25272,6 +26953,11 @@
       <c r="P337" t="n">
         <v>-70.67062</v>
       </c>
+      <c r="Q337" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=8295578</t>
+        </is>
+      </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
@@ -25344,6 +27030,11 @@
       <c r="P338" t="n">
         <v>-71.421233</v>
       </c>
+      <c r="Q338" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=8225857</t>
+        </is>
+      </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
@@ -25416,6 +27107,11 @@
       <c r="P339" t="n">
         <v>-70.918256</v>
       </c>
+      <c r="Q339" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=8278366</t>
+        </is>
+      </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
@@ -25488,6 +27184,11 @@
       <c r="P340" t="n">
         <v>-70.641706</v>
       </c>
+      <c r="Q340" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=8266155</t>
+        </is>
+      </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
@@ -25560,6 +27261,11 @@
       <c r="P341" t="n">
         <v>-68.92689900000001</v>
       </c>
+      <c r="Q341" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=8230878</t>
+        </is>
+      </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
@@ -25632,6 +27338,11 @@
       <c r="P342" t="n">
         <v>-69.936661</v>
       </c>
+      <c r="Q342" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=8219217</t>
+        </is>
+      </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
@@ -25704,6 +27415,11 @@
       <c r="P343" t="n">
         <v>-71.256238</v>
       </c>
+      <c r="Q343" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=8212936</t>
+        </is>
+      </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
@@ -25776,6 +27492,11 @@
       <c r="P344" t="n">
         <v>-70.24199900000001</v>
       </c>
+      <c r="Q344" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=8078731</t>
+        </is>
+      </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
@@ -25848,6 +27569,11 @@
       <c r="P345" t="n">
         <v>-70.66122900000001</v>
       </c>
+      <c r="Q345" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=8099693</t>
+        </is>
+      </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
@@ -25920,6 +27646,11 @@
       <c r="P346" t="n">
         <v>-70.13333799999999</v>
       </c>
+      <c r="Q346" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=8116988</t>
+        </is>
+      </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
@@ -25992,6 +27723,11 @@
       <c r="P347" t="n">
         <v>-70.911165</v>
       </c>
+      <c r="Q347" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=8041880</t>
+        </is>
+      </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
@@ -26064,6 +27800,11 @@
       <c r="P348" t="n">
         <v>-69.877286</v>
       </c>
+      <c r="Q348" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=8037100</t>
+        </is>
+      </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
@@ -26136,6 +27877,11 @@
       <c r="P349" t="n">
         <v>-70.233799</v>
       </c>
+      <c r="Q349" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=7964389</t>
+        </is>
+      </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
@@ -26208,6 +27954,11 @@
       <c r="P350" t="n">
         <v>-70.401471</v>
       </c>
+      <c r="Q350" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=7966606</t>
+        </is>
+      </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
@@ -26280,6 +28031,11 @@
       <c r="P351" t="n">
         <v>-70.108408</v>
       </c>
+      <c r="Q351" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=7957187</t>
+        </is>
+      </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
@@ -26352,6 +28108,11 @@
       <c r="P352" t="n">
         <v>-70.40146799999999</v>
       </c>
+      <c r="Q352" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=7913699</t>
+        </is>
+      </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
@@ -26424,6 +28185,11 @@
       <c r="P353" t="n">
         <v>-70.315686</v>
       </c>
+      <c r="Q353" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=7942747</t>
+        </is>
+      </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
@@ -26496,6 +28262,11 @@
       <c r="P354" t="n">
         <v>-71.09751300000001</v>
       </c>
+      <c r="Q354" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=7895431</t>
+        </is>
+      </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
@@ -26568,6 +28339,11 @@
       <c r="P355" t="n">
         <v>-70.838159</v>
       </c>
+      <c r="Q355" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=7915792</t>
+        </is>
+      </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
@@ -26640,6 +28416,11 @@
       <c r="P356" t="n">
         <v>-70.28232300000001</v>
       </c>
+      <c r="Q356" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=7915870</t>
+        </is>
+      </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
@@ -26712,6 +28493,11 @@
       <c r="P357" t="n">
         <v>-70.773015</v>
       </c>
+      <c r="Q357" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=7902744</t>
+        </is>
+      </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
@@ -26784,6 +28570,11 @@
       <c r="P358" t="n">
         <v>-70.37253</v>
       </c>
+      <c r="Q358" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=7893213</t>
+        </is>
+      </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
@@ -26856,6 +28647,11 @@
       <c r="P359" t="n">
         <v>-70.070944</v>
       </c>
+      <c r="Q359" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=7766713</t>
+        </is>
+      </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
@@ -26928,6 +28724,11 @@
       <c r="P360" t="n">
         <v>-70.890333</v>
       </c>
+      <c r="Q360" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=7763850</t>
+        </is>
+      </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
@@ -27000,6 +28801,11 @@
       <c r="P361" t="n">
         <v>-70.39232</v>
       </c>
+      <c r="Q361" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=7723012</t>
+        </is>
+      </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
@@ -27072,6 +28878,11 @@
       <c r="P362" t="n">
         <v>-70.810828</v>
       </c>
+      <c r="Q362" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=7642992</t>
+        </is>
+      </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
@@ -27144,6 +28955,11 @@
       <c r="P363" t="n">
         <v>-70.922513</v>
       </c>
+      <c r="Q363" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=7684373</t>
+        </is>
+      </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
@@ -27216,6 +29032,11 @@
       <c r="P364" t="n">
         <v>-70.149519</v>
       </c>
+      <c r="Q364" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=7663445</t>
+        </is>
+      </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
@@ -27288,6 +29109,11 @@
       <c r="P365" t="n">
         <v>-70.02141399999999</v>
       </c>
+      <c r="Q365" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=7657428</t>
+        </is>
+      </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
@@ -27360,6 +29186,11 @@
       <c r="P366" t="n">
         <v>-70.767681</v>
       </c>
+      <c r="Q366" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=7603955</t>
+        </is>
+      </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
@@ -27432,6 +29263,11 @@
       <c r="P367" t="n">
         <v>-69.07047300000001</v>
       </c>
+      <c r="Q367" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=7569133</t>
+        </is>
+      </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
@@ -27504,6 +29340,11 @@
       <c r="P368" t="n">
         <v>-70.412221</v>
       </c>
+      <c r="Q368" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=7510189</t>
+        </is>
+      </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
@@ -27576,6 +29417,11 @@
       <c r="P369" t="n">
         <v>-70.16467</v>
       </c>
+      <c r="Q369" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=7550308</t>
+        </is>
+      </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
@@ -27648,6 +29494,11 @@
       <c r="P370" t="n">
         <v>-70.383363</v>
       </c>
+      <c r="Q370" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=7539903</t>
+        </is>
+      </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
@@ -27720,6 +29571,11 @@
       <c r="P371" t="n">
         <v>-70.163556</v>
       </c>
+      <c r="Q371" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=7540033</t>
+        </is>
+      </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
@@ -27792,6 +29648,11 @@
       <c r="P372" t="n">
         <v>-70.808122</v>
       </c>
+      <c r="Q372" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=7512814</t>
+        </is>
+      </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
@@ -27864,6 +29725,11 @@
       <c r="P373" t="n">
         <v>-69.044974</v>
       </c>
+      <c r="Q373" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=7479241</t>
+        </is>
+      </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
@@ -27936,6 +29802,11 @@
       <c r="P374" t="n">
         <v>-70.387579</v>
       </c>
+      <c r="Q374" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=7448681</t>
+        </is>
+      </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
@@ -28008,6 +29879,11 @@
       <c r="P375" t="n">
         <v>-71.45433800000001</v>
       </c>
+      <c r="Q375" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=7342800</t>
+        </is>
+      </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
@@ -28080,6 +29956,11 @@
       <c r="P376" t="n">
         <v>-71.159175</v>
       </c>
+      <c r="Q376" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=7379120</t>
+        </is>
+      </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
@@ -28152,6 +30033,11 @@
       <c r="P377" t="n">
         <v>-70.69389700000001</v>
       </c>
+      <c r="Q377" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=7314037</t>
+        </is>
+      </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
@@ -28224,6 +30110,11 @@
       <c r="P378" t="n">
         <v>-70.418425</v>
       </c>
+      <c r="Q378" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=7309008</t>
+        </is>
+      </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
@@ -28296,6 +30187,11 @@
       <c r="P379" t="n">
         <v>-70.21296</v>
       </c>
+      <c r="Q379" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=7280498</t>
+        </is>
+      </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
@@ -28368,6 +30264,11 @@
       <c r="P380" t="n">
         <v>-70.90496400000001</v>
       </c>
+      <c r="Q380" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=7264751</t>
+        </is>
+      </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
@@ -28440,6 +30341,11 @@
       <c r="P381" t="n">
         <v>-70.044442</v>
       </c>
+      <c r="Q381" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=7271603</t>
+        </is>
+      </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
@@ -28512,6 +30418,11 @@
       <c r="P382" t="n">
         <v>-69.670259</v>
       </c>
+      <c r="Q382" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=7218754</t>
+        </is>
+      </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
@@ -28584,6 +30495,11 @@
       <c r="P383" t="n">
         <v>-69.478999</v>
       </c>
+      <c r="Q383" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=7234104</t>
+        </is>
+      </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
@@ -28656,6 +30572,11 @@
       <c r="P384" t="n">
         <v>-70.606973</v>
       </c>
+      <c r="Q384" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=7187238</t>
+        </is>
+      </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
@@ -28728,6 +30649,11 @@
       <c r="P385" t="n">
         <v>-70.07522899999999</v>
       </c>
+      <c r="Q385" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=7123251</t>
+        </is>
+      </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
@@ -28800,6 +30726,11 @@
       <c r="P386" t="n">
         <v>-71.21355800000001</v>
       </c>
+      <c r="Q386" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=7060853</t>
+        </is>
+      </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
@@ -28872,6 +30803,11 @@
       <c r="P387" t="n">
         <v>-71.072934</v>
       </c>
+      <c r="Q387" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=6998330</t>
+        </is>
+      </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
@@ -28944,6 +30880,11 @@
       <c r="P388" t="n">
         <v>-69.96878</v>
       </c>
+      <c r="Q388" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=6921000</t>
+        </is>
+      </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
@@ -29016,6 +30957,11 @@
       <c r="P389" t="n">
         <v>-70.267605</v>
       </c>
+      <c r="Q389" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=6903315</t>
+        </is>
+      </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
@@ -29088,6 +31034,11 @@
       <c r="P390" t="n">
         <v>-71.446123</v>
       </c>
+      <c r="Q390" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=6772270</t>
+        </is>
+      </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
@@ -29160,6 +31111,11 @@
       <c r="P391" t="n">
         <v>-69.883824</v>
       </c>
+      <c r="Q391" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=6793954</t>
+        </is>
+      </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
@@ -29232,6 +31188,11 @@
       <c r="P392" t="n">
         <v>-70.277699</v>
       </c>
+      <c r="Q392" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=6759079</t>
+        </is>
+      </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
@@ -29304,6 +31265,11 @@
       <c r="P393" t="n">
         <v>-70.038954</v>
       </c>
+      <c r="Q393" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=6739043</t>
+        </is>
+      </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
@@ -29376,6 +31342,11 @@
       <c r="P394" t="n">
         <v>-71.45647099999999</v>
       </c>
+      <c r="Q394" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=6723948</t>
+        </is>
+      </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
@@ -29448,6 +31419,11 @@
       <c r="P395" t="n">
         <v>-70.64572099999999</v>
       </c>
+      <c r="Q395" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=6692268</t>
+        </is>
+      </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
@@ -29520,6 +31496,11 @@
       <c r="P396" t="n">
         <v>-71.44181500000001</v>
       </c>
+      <c r="Q396" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=6642205</t>
+        </is>
+      </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
@@ -29592,6 +31573,11 @@
       <c r="P397" t="n">
         <v>-69.902556</v>
       </c>
+      <c r="Q397" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=6630762</t>
+        </is>
+      </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
@@ -29664,6 +31650,11 @@
       <c r="P398" t="n">
         <v>-70.783221</v>
       </c>
+      <c r="Q398" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=6592631</t>
+        </is>
+      </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
@@ -29736,6 +31727,11 @@
       <c r="P399" t="n">
         <v>-70.77395199999999</v>
       </c>
+      <c r="Q399" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=6588721</t>
+        </is>
+      </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
@@ -29808,6 +31804,11 @@
       <c r="P400" t="n">
         <v>-70.78176499999999</v>
       </c>
+      <c r="Q400" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=6572475</t>
+        </is>
+      </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
@@ -29880,6 +31881,11 @@
       <c r="P401" t="n">
         <v>-69.3794</v>
       </c>
+      <c r="Q401" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=6562838</t>
+        </is>
+      </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
@@ -29952,6 +31958,11 @@
       <c r="P402" t="n">
         <v>-70.251034</v>
       </c>
+      <c r="Q402" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=6530120</t>
+        </is>
+      </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
@@ -30024,6 +32035,11 @@
       <c r="P403" t="n">
         <v>-70.245693</v>
       </c>
+      <c r="Q403" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=6511794</t>
+        </is>
+      </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
@@ -30096,6 +32112,11 @@
       <c r="P404" t="n">
         <v>-69.425909</v>
       </c>
+      <c r="Q404" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=6353048</t>
+        </is>
+      </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
@@ -30168,6 +32189,11 @@
       <c r="P405" t="n">
         <v>-69.50999400000001</v>
       </c>
+      <c r="Q405" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=6462729</t>
+        </is>
+      </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
@@ -30240,6 +32266,11 @@
       <c r="P406" t="n">
         <v>-69.195967</v>
       </c>
+      <c r="Q406" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=6441840</t>
+        </is>
+      </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
@@ -30312,6 +32343,11 @@
       <c r="P407" t="n">
         <v>-70.328903</v>
       </c>
+      <c r="Q407" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=6394484</t>
+        </is>
+      </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
@@ -30384,6 +32420,11 @@
       <c r="P408" t="n">
         <v>-69.253997</v>
       </c>
+      <c r="Q408" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=6373086</t>
+        </is>
+      </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
@@ -30456,6 +32497,11 @@
       <c r="P409" t="n">
         <v>-68.63726699999999</v>
       </c>
+      <c r="Q409" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=6326647</t>
+        </is>
+      </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
@@ -30528,6 +32574,11 @@
       <c r="P410" t="n">
         <v>-69.483298</v>
       </c>
+      <c r="Q410" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=6337179</t>
+        </is>
+      </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
@@ -30600,6 +32651,11 @@
       <c r="P411" t="n">
         <v>-70.415499</v>
       </c>
+      <c r="Q411" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=6337545</t>
+        </is>
+      </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
@@ -30672,6 +32728,11 @@
       <c r="P412" t="n">
         <v>-69.556451</v>
       </c>
+      <c r="Q412" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=6309095</t>
+        </is>
+      </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
@@ -30744,6 +32805,11 @@
       <c r="P413" t="n">
         <v>-70.80624899999999</v>
       </c>
+      <c r="Q413" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=6299593</t>
+        </is>
+      </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
@@ -30816,6 +32882,11 @@
       <c r="P414" t="n">
         <v>-70.608502</v>
       </c>
+      <c r="Q414" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=6280528</t>
+        </is>
+      </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
@@ -30888,6 +32959,11 @@
       <c r="P415" t="n">
         <v>-70.313479</v>
       </c>
+      <c r="Q415" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=6287168</t>
+        </is>
+      </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
@@ -30960,6 +33036,11 @@
       <c r="P416" t="n">
         <v>-69.59756899999999</v>
       </c>
+      <c r="Q416" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=6236248</t>
+        </is>
+      </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
@@ -31032,6 +33113,11 @@
       <c r="P417" t="n">
         <v>-70.694425</v>
       </c>
+      <c r="Q417" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=6188637</t>
+        </is>
+      </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
@@ -31104,6 +33190,11 @@
       <c r="P418" t="n">
         <v>-70.814106</v>
       </c>
+      <c r="Q418" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=6191089</t>
+        </is>
+      </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
@@ -31176,6 +33267,11 @@
       <c r="P419" t="n">
         <v>-71.24435</v>
       </c>
+      <c r="Q419" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=6195347</t>
+        </is>
+      </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
@@ -31248,6 +33344,11 @@
       <c r="P420" t="n">
         <v>-70.265428</v>
       </c>
+      <c r="Q420" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=6153671</t>
+        </is>
+      </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
@@ -31320,6 +33421,11 @@
       <c r="P421" t="n">
         <v>-69.981533</v>
       </c>
+      <c r="Q421" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=6122195</t>
+        </is>
+      </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
@@ -31392,6 +33498,11 @@
       <c r="P422" t="n">
         <v>-70.31099</v>
       </c>
+      <c r="Q422" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=6107544</t>
+        </is>
+      </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
@@ -31464,6 +33575,11 @@
       <c r="P423" t="n">
         <v>-71.441974</v>
       </c>
+      <c r="Q423" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=6079447</t>
+        </is>
+      </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
@@ -31536,6 +33652,11 @@
       <c r="P424" t="n">
         <v>-70.26781099999999</v>
       </c>
+      <c r="Q424" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=6049283</t>
+        </is>
+      </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
@@ -31608,6 +33729,11 @@
       <c r="P425" t="n">
         <v>-70.8445</v>
       </c>
+      <c r="Q425" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=6016381</t>
+        </is>
+      </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
@@ -31680,6 +33806,11 @@
       <c r="P426" t="n">
         <v>-71.086629</v>
       </c>
+      <c r="Q426" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=5958860</t>
+        </is>
+      </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
@@ -31752,6 +33883,11 @@
       <c r="P427" t="n">
         <v>-69.12329</v>
       </c>
+      <c r="Q427" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=5938135</t>
+        </is>
+      </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
@@ -31824,6 +33960,11 @@
       <c r="P428" t="n">
         <v>-70.23864500000001</v>
       </c>
+      <c r="Q428" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=5914637</t>
+        </is>
+      </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
@@ -31896,6 +34037,11 @@
       <c r="P429" t="n">
         <v>-70.908942</v>
       </c>
+      <c r="Q429" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=5914637</t>
+        </is>
+      </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
@@ -31968,6 +34114,11 @@
       <c r="P430" t="n">
         <v>-70.836522</v>
       </c>
+      <c r="Q430" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=5901314</t>
+        </is>
+      </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
@@ -32040,6 +34191,11 @@
       <c r="P431" t="n">
         <v>-70.72020000000001</v>
       </c>
+      <c r="Q431" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=5883091</t>
+        </is>
+      </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
@@ -32112,6 +34268,11 @@
       <c r="P432" t="n">
         <v>-70.33778700000001</v>
       </c>
+      <c r="Q432" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=5871667</t>
+        </is>
+      </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
@@ -32184,6 +34345,11 @@
       <c r="P433" t="n">
         <v>-70.315561</v>
       </c>
+      <c r="Q433" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=5876953</t>
+        </is>
+      </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
@@ -32256,6 +34422,11 @@
       <c r="P434" t="n">
         <v>-70.898945</v>
       </c>
+      <c r="Q434" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=5878186</t>
+        </is>
+      </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
@@ -32328,6 +34499,11 @@
       <c r="P435" t="n">
         <v>-71.105513</v>
       </c>
+      <c r="Q435" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=5872704</t>
+        </is>
+      </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
@@ -32400,6 +34576,11 @@
       <c r="P436" t="n">
         <v>-69.263999</v>
       </c>
+      <c r="Q436" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=5854758</t>
+        </is>
+      </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
@@ -32472,6 +34653,11 @@
       <c r="P437" t="n">
         <v>-70.38323800000001</v>
       </c>
+      <c r="Q437" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=5864428</t>
+        </is>
+      </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
@@ -32544,6 +34730,11 @@
       <c r="P438" t="n">
         <v>-69.175501</v>
       </c>
+      <c r="Q438" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=5833717</t>
+        </is>
+      </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
@@ -32616,6 +34807,11 @@
       <c r="P439" t="n">
         <v>-70.803017</v>
       </c>
+      <c r="Q439" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=5818924</t>
+        </is>
+      </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
@@ -32688,6 +34884,11 @@
       <c r="P440" t="n">
         <v>-70.255127</v>
       </c>
+      <c r="Q440" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=5820294</t>
+        </is>
+      </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
@@ -32760,6 +34961,11 @@
       <c r="P441" t="n">
         <v>-70.751096</v>
       </c>
+      <c r="Q441" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=5800829</t>
+        </is>
+      </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
@@ -32832,6 +35038,11 @@
       <c r="P442" t="n">
         <v>-71.03282</v>
       </c>
+      <c r="Q442" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=5749481</t>
+        </is>
+      </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
@@ -32904,6 +35115,11 @@
       <c r="P443" t="n">
         <v>-69.481178</v>
       </c>
+      <c r="Q443" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=5702838</t>
+        </is>
+      </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
@@ -32976,6 +35192,11 @@
       <c r="P444" t="n">
         <v>-70.81770299999999</v>
       </c>
+      <c r="Q444" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=5724713</t>
+        </is>
+      </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
@@ -33048,6 +35269,11 @@
       <c r="P445" t="n">
         <v>-69.478813</v>
       </c>
+      <c r="Q445" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=5727262</t>
+        </is>
+      </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
@@ -33120,6 +35346,11 @@
       <c r="P446" t="n">
         <v>-70.40315099999999</v>
       </c>
+      <c r="Q446" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=5670887</t>
+        </is>
+      </c>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
@@ -33192,6 +35423,11 @@
       <c r="P447" t="n">
         <v>-70.09433199999999</v>
       </c>
+      <c r="Q447" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=5678505</t>
+        </is>
+      </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
@@ -33264,6 +35500,11 @@
       <c r="P448" t="n">
         <v>-70.83379499999999</v>
       </c>
+      <c r="Q448" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=5644788</t>
+        </is>
+      </c>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
@@ -33336,6 +35577,11 @@
       <c r="P449" t="n">
         <v>-70.692126</v>
       </c>
+      <c r="Q449" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=5634499</t>
+        </is>
+      </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
@@ -33408,6 +35654,11 @@
       <c r="P450" t="n">
         <v>-69.22079600000001</v>
       </c>
+      <c r="Q450" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=5614517</t>
+        </is>
+      </c>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
@@ -33480,6 +35731,11 @@
       <c r="P451" t="n">
         <v>-70.33148199999999</v>
       </c>
+      <c r="Q451" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=5580514</t>
+        </is>
+      </c>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
@@ -33552,6 +35808,11 @@
       <c r="P452" t="n">
         <v>-70.110028</v>
       </c>
+      <c r="Q452" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=5540185</t>
+        </is>
+      </c>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
@@ -33624,6 +35885,11 @@
       <c r="P453" t="n">
         <v>-70.15494200000001</v>
       </c>
+      <c r="Q453" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=5459944</t>
+        </is>
+      </c>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
@@ -33696,6 +35962,11 @@
       <c r="P454" t="n">
         <v>-70.264409</v>
       </c>
+      <c r="Q454" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=5440479</t>
+        </is>
+      </c>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
@@ -33768,6 +36039,11 @@
       <c r="P455" t="n">
         <v>-70.107815</v>
       </c>
+      <c r="Q455" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=5371120</t>
+        </is>
+      </c>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
@@ -33840,6 +36116,11 @@
       <c r="P456" t="n">
         <v>-70.860767</v>
       </c>
+      <c r="Q456" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=5367003</t>
+        </is>
+      </c>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
@@ -33912,6 +36193,11 @@
       <c r="P457" t="n">
         <v>-70.735043</v>
       </c>
+      <c r="Q457" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=5340200</t>
+        </is>
+      </c>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
@@ -34056,6 +36342,11 @@
       <c r="P459" t="n">
         <v>-71.093369</v>
       </c>
+      <c r="Q459" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=5300827</t>
+        </is>
+      </c>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
@@ -34128,6 +36419,11 @@
       <c r="P460" t="n">
         <v>-70.26907799999999</v>
       </c>
+      <c r="Q460" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=5301508</t>
+        </is>
+      </c>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
@@ -34200,6 +36496,11 @@
       <c r="P461" t="n">
         <v>-70.06363</v>
       </c>
+      <c r="Q461" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=5301825</t>
+        </is>
+      </c>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
@@ -34272,6 +36573,11 @@
       <c r="P462" t="n">
         <v>-70.373115</v>
       </c>
+      <c r="Q462" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=5302149</t>
+        </is>
+      </c>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr">
@@ -34344,6 +36650,11 @@
       <c r="P463" t="n">
         <v>-70.14481499999999</v>
       </c>
+      <c r="Q463" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=5287120</t>
+        </is>
+      </c>
     </row>
     <row r="464">
       <c r="A464" t="inlineStr">
@@ -34416,6 +36727,11 @@
       <c r="P464" t="n">
         <v>-70.245287</v>
       </c>
+      <c r="Q464" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=5202994</t>
+        </is>
+      </c>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr">
@@ -34488,6 +36804,11 @@
       <c r="P465" t="n">
         <v>-70.431915</v>
       </c>
+      <c r="Q465" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=5206097</t>
+        </is>
+      </c>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
@@ -34560,6 +36881,11 @@
       <c r="P466" t="n">
         <v>-70.837627</v>
       </c>
+      <c r="Q466" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=5203489</t>
+        </is>
+      </c>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
@@ -34632,6 +36958,11 @@
       <c r="P467" t="n">
         <v>-70.814879</v>
       </c>
+      <c r="Q467" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=5168268</t>
+        </is>
+      </c>
     </row>
     <row r="468">
       <c r="A468" t="inlineStr">
@@ -34704,6 +37035,11 @@
       <c r="P468" t="n">
         <v>-70.210919</v>
       </c>
+      <c r="Q468" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=5170477</t>
+        </is>
+      </c>
     </row>
     <row r="469">
       <c r="A469" t="inlineStr">
@@ -34776,6 +37112,11 @@
       <c r="P469" t="n">
         <v>-69.480829</v>
       </c>
+      <c r="Q469" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=5153524</t>
+        </is>
+      </c>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
@@ -34848,6 +37189,11 @@
       <c r="P470" t="n">
         <v>-70.403165</v>
       </c>
+      <c r="Q470" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=5016531</t>
+        </is>
+      </c>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
@@ -34920,6 +37266,11 @@
       <c r="P471" t="n">
         <v>-70.401026</v>
       </c>
+      <c r="Q471" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=5122475</t>
+        </is>
+      </c>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
@@ -34992,6 +37343,11 @@
       <c r="P472" t="n">
         <v>-70.767961</v>
       </c>
+      <c r="Q472" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=5107307</t>
+        </is>
+      </c>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
@@ -35064,6 +37420,11 @@
       <c r="P473" t="n">
         <v>-70.620846</v>
       </c>
+      <c r="Q473" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=5081291</t>
+        </is>
+      </c>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
@@ -35136,6 +37497,11 @@
       <c r="P474" t="n">
         <v>-69.483298</v>
       </c>
+      <c r="Q474" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=5077014</t>
+        </is>
+      </c>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
@@ -35208,6 +37574,11 @@
       <c r="P475" t="n">
         <v>-70.298096</v>
       </c>
+      <c r="Q475" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=5067224</t>
+        </is>
+      </c>
     </row>
     <row r="476">
       <c r="A476" t="inlineStr">
@@ -35280,6 +37651,11 @@
       <c r="P476" t="n">
         <v>-70.316997</v>
       </c>
+      <c r="Q476" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=5012889</t>
+        </is>
+      </c>
     </row>
     <row r="477">
       <c r="A477" t="inlineStr">
@@ -35352,6 +37728,11 @@
       <c r="P477" t="n">
         <v>-70.41565</v>
       </c>
+      <c r="Q477" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=5024643</t>
+        </is>
+      </c>
     </row>
     <row r="478">
       <c r="A478" t="inlineStr">
@@ -35424,6 +37805,11 @@
       <c r="P478" t="n">
         <v>-70.264498</v>
       </c>
+      <c r="Q478" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=5012824</t>
+        </is>
+      </c>
     </row>
     <row r="479">
       <c r="A479" t="inlineStr">
@@ -35496,6 +37882,11 @@
       <c r="P479" t="n">
         <v>-70.924533</v>
       </c>
+      <c r="Q479" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=4965961</t>
+        </is>
+      </c>
     </row>
     <row r="480">
       <c r="A480" t="inlineStr">
@@ -35568,6 +37959,11 @@
       <c r="P480" t="n">
         <v>-70.768766</v>
       </c>
+      <c r="Q480" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=4909244</t>
+        </is>
+      </c>
     </row>
     <row r="481">
       <c r="A481" t="inlineStr">
@@ -35640,6 +38036,11 @@
       <c r="P481" t="n">
         <v>-69.06989299999999</v>
       </c>
+      <c r="Q481" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=4896050</t>
+        </is>
+      </c>
     </row>
     <row r="482">
       <c r="A482" t="inlineStr">
@@ -35712,6 +38113,11 @@
       <c r="P482" t="n">
         <v>-70.86456200000001</v>
       </c>
+      <c r="Q482" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=4868907</t>
+        </is>
+      </c>
     </row>
     <row r="483">
       <c r="A483" t="inlineStr">
@@ -35784,6 +38190,11 @@
       <c r="P483" t="n">
         <v>-70.213819</v>
       </c>
+      <c r="Q483" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=4838388</t>
+        </is>
+      </c>
     </row>
     <row r="484">
       <c r="A484" t="inlineStr">
@@ -35856,6 +38267,11 @@
       <c r="P484" t="n">
         <v>-70.843756</v>
       </c>
+      <c r="Q484" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=4855545</t>
+        </is>
+      </c>
     </row>
     <row r="485">
       <c r="A485" t="inlineStr">
@@ -35928,6 +38344,11 @@
       <c r="P485" t="n">
         <v>-69.28292399999999</v>
       </c>
+      <c r="Q485" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=4804419</t>
+        </is>
+      </c>
     </row>
     <row r="486">
       <c r="A486" t="inlineStr">
@@ -36000,6 +38421,11 @@
       <c r="P486" t="n">
         <v>-70.321348</v>
       </c>
+      <c r="Q486" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=4804490</t>
+        </is>
+      </c>
     </row>
     <row r="487">
       <c r="A487" t="inlineStr">
@@ -36072,6 +38498,11 @@
       <c r="P487" t="n">
         <v>-70.84268299999999</v>
       </c>
+      <c r="Q487" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=4790073</t>
+        </is>
+      </c>
     </row>
     <row r="488">
       <c r="A488" t="inlineStr">
@@ -36144,6 +38575,11 @@
       <c r="P488" t="n">
         <v>-70.813142</v>
       </c>
+      <c r="Q488" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=4792157</t>
+        </is>
+      </c>
     </row>
     <row r="489">
       <c r="A489" t="inlineStr">
@@ -36216,6 +38652,11 @@
       <c r="P489" t="n">
         <v>-70.335148</v>
       </c>
+      <c r="Q489" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=4786508</t>
+        </is>
+      </c>
     </row>
     <row r="490">
       <c r="A490" t="inlineStr">
@@ -36288,6 +38729,11 @@
       <c r="P490" t="n">
         <v>-70.78031900000001</v>
       </c>
+      <c r="Q490" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=4743865</t>
+        </is>
+      </c>
     </row>
     <row r="491">
       <c r="A491" t="inlineStr">
@@ -36360,6 +38806,11 @@
       <c r="P491" t="n">
         <v>-70.667401</v>
       </c>
+      <c r="Q491" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=4754889</t>
+        </is>
+      </c>
     </row>
     <row r="492">
       <c r="A492" t="inlineStr">
@@ -36432,6 +38883,11 @@
       <c r="P492" t="n">
         <v>-70.14688</v>
       </c>
+      <c r="Q492" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=4680343</t>
+        </is>
+      </c>
     </row>
     <row r="493">
       <c r="A493" t="inlineStr">
@@ -36504,6 +38960,11 @@
       <c r="P493" t="n">
         <v>-70.18083</v>
       </c>
+      <c r="Q493" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=4663138</t>
+        </is>
+      </c>
     </row>
     <row r="494">
       <c r="A494" t="inlineStr">
@@ -36576,6 +39037,11 @@
       <c r="P494" t="n">
         <v>-69.576418</v>
       </c>
+      <c r="Q494" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=4661937</t>
+        </is>
+      </c>
     </row>
     <row r="495">
       <c r="A495" t="inlineStr">
@@ -36648,6 +39114,11 @@
       <c r="P495" t="n">
         <v>-69.770808</v>
       </c>
+      <c r="Q495" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=4672647</t>
+        </is>
+      </c>
     </row>
     <row r="496">
       <c r="A496" t="inlineStr">
@@ -36720,6 +39191,11 @@
       <c r="P496" t="n">
         <v>-70.20384799999999</v>
       </c>
+      <c r="Q496" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=4657683</t>
+        </is>
+      </c>
     </row>
     <row r="497">
       <c r="A497" t="inlineStr">
@@ -36792,6 +39268,11 @@
       <c r="P497" t="n">
         <v>-69.431624</v>
       </c>
+      <c r="Q497" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=4643426</t>
+        </is>
+      </c>
     </row>
     <row r="498">
       <c r="A498" t="inlineStr">
@@ -36864,6 +39345,11 @@
       <c r="P498" t="n">
         <v>-70.31296399999999</v>
       </c>
+      <c r="Q498" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=4628721</t>
+        </is>
+      </c>
     </row>
     <row r="499">
       <c r="A499" t="inlineStr">
@@ -36936,6 +39422,11 @@
       <c r="P499" t="n">
         <v>-70.369708</v>
       </c>
+      <c r="Q499" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=4626114</t>
+        </is>
+      </c>
     </row>
     <row r="500">
       <c r="A500" t="inlineStr">
@@ -37008,6 +39499,11 @@
       <c r="P500" t="n">
         <v>-70.952111</v>
       </c>
+      <c r="Q500" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=4621161</t>
+        </is>
+      </c>
     </row>
     <row r="501">
       <c r="A501" t="inlineStr">
@@ -37080,6 +39576,11 @@
       <c r="P501" t="n">
         <v>-70.691356</v>
       </c>
+      <c r="Q501" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=4601690</t>
+        </is>
+      </c>
     </row>
     <row r="502">
       <c r="A502" t="inlineStr">
@@ -37152,6 +39653,11 @@
       <c r="P502" t="n">
         <v>-70.698009</v>
       </c>
+      <c r="Q502" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=4604735</t>
+        </is>
+      </c>
     </row>
     <row r="503">
       <c r="A503" t="inlineStr">
@@ -37224,6 +39730,11 @@
       <c r="P503" t="n">
         <v>-70.092769</v>
       </c>
+      <c r="Q503" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=4593841</t>
+        </is>
+      </c>
     </row>
     <row r="504">
       <c r="A504" t="inlineStr">
@@ -37296,6 +39807,11 @@
       <c r="P504" t="n">
         <v>-70.43472800000001</v>
       </c>
+      <c r="Q504" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=4583151</t>
+        </is>
+      </c>
     </row>
     <row r="505">
       <c r="A505" t="inlineStr">
@@ -37368,6 +39884,11 @@
       <c r="P505" t="n">
         <v>-70.84587999999999</v>
       </c>
+      <c r="Q505" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=4572886</t>
+        </is>
+      </c>
     </row>
     <row r="506">
       <c r="A506" t="inlineStr">
@@ -37440,6 +39961,11 @@
       <c r="P506" t="n">
         <v>-69.030334</v>
       </c>
+      <c r="Q506" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=4562942</t>
+        </is>
+      </c>
     </row>
     <row r="507">
       <c r="A507" t="inlineStr">
@@ -37512,6 +40038,11 @@
       <c r="P507" t="n">
         <v>-70.136719</v>
       </c>
+      <c r="Q507" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=4545177</t>
+        </is>
+      </c>
     </row>
     <row r="508">
       <c r="A508" t="inlineStr">
@@ -37584,6 +40115,11 @@
       <c r="P508" t="n">
         <v>-70.344674</v>
       </c>
+      <c r="Q508" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=4527073</t>
+        </is>
+      </c>
     </row>
     <row r="509">
       <c r="A509" t="inlineStr">
@@ -37656,6 +40192,11 @@
       <c r="P509" t="n">
         <v>-70.351805</v>
       </c>
+      <c r="Q509" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=4473785</t>
+        </is>
+      </c>
     </row>
     <row r="510">
       <c r="A510" t="inlineStr">
@@ -37728,6 +40269,11 @@
       <c r="P510" t="n">
         <v>-70.90769899999999</v>
       </c>
+      <c r="Q510" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=4440357</t>
+        </is>
+      </c>
     </row>
     <row r="511">
       <c r="A511" t="inlineStr">
@@ -37800,6 +40346,11 @@
       <c r="P511" t="n">
         <v>-70.409617</v>
       </c>
+      <c r="Q511" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=4419889</t>
+        </is>
+      </c>
     </row>
     <row r="512">
       <c r="A512" t="inlineStr">
@@ -37872,6 +40423,11 @@
       <c r="P512" t="n">
         <v>-70.221782</v>
       </c>
+      <c r="Q512" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=4389558</t>
+        </is>
+      </c>
     </row>
     <row r="513">
       <c r="A513" t="inlineStr">
@@ -37944,6 +40500,11 @@
       <c r="P513" t="n">
         <v>-70.338083</v>
       </c>
+      <c r="Q513" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=4398248</t>
+        </is>
+      </c>
     </row>
     <row r="514">
       <c r="A514" t="inlineStr">
@@ -38016,6 +40577,11 @@
       <c r="P514" t="n">
         <v>-70.15150300000001</v>
       </c>
+      <c r="Q514" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=4395947</t>
+        </is>
+      </c>
     </row>
     <row r="515">
       <c r="A515" t="inlineStr">
@@ -38088,6 +40654,11 @@
       <c r="P515" t="n">
         <v>-70.23909399999999</v>
       </c>
+      <c r="Q515" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=4340837</t>
+        </is>
+      </c>
     </row>
     <row r="516">
       <c r="A516" t="inlineStr">
@@ -38159,6 +40730,11 @@
       </c>
       <c r="P516" t="n">
         <v>-69.029284</v>
+      </c>
+      <c r="Q516" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/elementosFisicos/enviados.php?id_documento=4330234</t>
+        </is>
       </c>
     </row>
   </sheetData>
